--- a/vag-rad/vag-rad_stats.xlsx
+++ b/vag-rad/vag-rad_stats.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="651">
   <si>
     <t>date</t>
   </si>
@@ -1884,6 +1884,18 @@
   </si>
   <si>
     <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>2025-02-17</t>
+  </si>
+  <si>
+    <t>2025-02-18</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
   </si>
   <si>
     <t>median_number_of_available_bikes</t>
@@ -2319,7 +2331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B620"/>
+  <dimension ref="A1:B624"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7280,6 +7292,38 @@
       </c>
       <c r="B620">
         <v>2011</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621" t="s">
+        <v>621</v>
+      </c>
+      <c r="B621">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622" t="s">
+        <v>622</v>
+      </c>
+      <c r="B622">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623" t="s">
+        <v>623</v>
+      </c>
+      <c r="B623">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624" t="s">
+        <v>624</v>
+      </c>
+      <c r="B624">
+        <v>2080</v>
       </c>
     </row>
   </sheetData>
@@ -7297,21 +7341,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B2">
         <v>1793</v>
@@ -7328,7 +7372,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B3">
         <v>1713.5</v>
@@ -7345,7 +7389,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B4">
         <v>1798</v>
@@ -7362,7 +7406,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B5">
         <v>1810</v>
@@ -7379,7 +7423,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B6">
         <v>1841.5</v>
@@ -7396,7 +7440,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B7">
         <v>1767</v>
@@ -7413,7 +7457,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B8">
         <v>1785</v>
@@ -7430,7 +7474,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B9">
         <v>1782</v>
@@ -7447,7 +7491,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B10">
         <v>1708</v>
@@ -7464,7 +7508,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B11">
         <v>1827.5</v>
@@ -7481,7 +7525,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B12">
         <v>2279</v>
@@ -7498,7 +7542,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B13">
         <v>2011.5</v>
@@ -7515,7 +7559,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B14">
         <v>2315</v>
@@ -7532,7 +7576,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B15">
         <v>2111</v>
@@ -7549,7 +7593,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B16">
         <v>2068</v>
@@ -7566,7 +7610,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B17">
         <v>2109</v>
@@ -7583,7 +7627,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B18">
         <v>2031.5</v>
@@ -7600,7 +7644,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B19">
         <v>2040</v>
@@ -7617,7 +7661,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B20">
         <v>1822</v>
@@ -7634,7 +7678,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B21">
         <v>1893</v>
@@ -7651,7 +7695,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B22">
         <v>1673</v>
@@ -7668,16 +7712,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B23">
-        <v>1924</v>
+        <v>1951</v>
       </c>
       <c r="C23">
-        <v>1913.4</v>
+        <v>1939.157894736842</v>
       </c>
       <c r="D23">
-        <v>2024</v>
+        <v>2080</v>
       </c>
       <c r="E23">
         <v>1733</v>
@@ -7690,7 +7734,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7707,6 +7751,38 @@
       </c>
       <c r="B2">
         <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>622</v>
+      </c>
+      <c r="B4">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>623</v>
+      </c>
+      <c r="B5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>624</v>
+      </c>
+      <c r="B6">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -7724,33 +7800,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C2">
-        <v>189</v>
+        <v>189.2</v>
       </c>
       <c r="D2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="E2">
-        <v>189</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -7760,7 +7836,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7777,6 +7853,38 @@
       </c>
       <c r="B2">
         <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>622</v>
+      </c>
+      <c r="B4">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>623</v>
+      </c>
+      <c r="B5">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>624</v>
+      </c>
+      <c r="B6">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -7794,33 +7902,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B2">
         <v>188</v>
       </c>
       <c r="C2">
-        <v>188</v>
+        <v>190.8</v>
       </c>
       <c r="D2">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="E2">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -7830,7 +7938,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7847,6 +7955,38 @@
       </c>
       <c r="B2">
         <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>622</v>
+      </c>
+      <c r="B4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>623</v>
+      </c>
+      <c r="B5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>624</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -7864,30 +8004,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2">
-        <v>28</v>
+        <v>29.4</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2">
         <v>28</v>

--- a/vag-rad/vag-rad_stats.xlsx
+++ b/vag-rad/vag-rad_stats.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="643">
   <si>
     <t>date</t>
   </si>
@@ -1898,6 +1898,12 @@
     <t>2025-02-19</t>
   </si>
   <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
     <t>median_number_of_available_bikes</t>
   </si>
   <si>
@@ -1910,70 +1916,40 @@
     <t>min_number_of_available_bikes</t>
   </si>
   <si>
-    <t>2023 May</t>
-  </si>
-  <si>
-    <t>2023 June</t>
-  </si>
-  <si>
-    <t>2023 July</t>
-  </si>
-  <si>
-    <t>2023 August</t>
-  </si>
-  <si>
-    <t>2023 September</t>
-  </si>
-  <si>
-    <t>2023 October</t>
-  </si>
-  <si>
-    <t>2023 November</t>
-  </si>
-  <si>
-    <t>2023 December</t>
-  </si>
-  <si>
-    <t>2024 January</t>
-  </si>
-  <si>
-    <t>2024 February</t>
-  </si>
-  <si>
-    <t>2024 March</t>
-  </si>
-  <si>
-    <t>2024 April</t>
-  </si>
-  <si>
-    <t>2024 May</t>
-  </si>
-  <si>
-    <t>2024 June</t>
-  </si>
-  <si>
-    <t>2024 July</t>
-  </si>
-  <si>
-    <t>2024 August</t>
-  </si>
-  <si>
-    <t>2024 September</t>
-  </si>
-  <si>
-    <t>2024 October</t>
-  </si>
-  <si>
-    <t>2024 November</t>
-  </si>
-  <si>
-    <t>2024 December</t>
-  </si>
-  <si>
-    <t>2025 January</t>
-  </si>
-  <si>
-    <t>2025 February</t>
+    <t>May</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>April</t>
   </si>
 </sst>
 </file>
@@ -7333,397 +7309,466 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
         <v>629</v>
       </c>
-      <c r="B2">
+      <c r="F1" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C2">
         <v>1793</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>1806</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>1873</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>1752</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>630</v>
-      </c>
-      <c r="B3">
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2023</v>
+      </c>
+      <c r="B3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C3">
         <v>1713.5</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1707.133333333333</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>1806</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>1623</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2023</v>
+      </c>
+      <c r="B4" t="s">
+        <v>633</v>
+      </c>
+      <c r="C4">
+        <v>1798</v>
+      </c>
+      <c r="D4">
+        <v>1783.870967741935</v>
+      </c>
+      <c r="E4">
+        <v>1885</v>
+      </c>
+      <c r="F4">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>2023</v>
+      </c>
+      <c r="B5" t="s">
+        <v>634</v>
+      </c>
+      <c r="C5">
+        <v>1810</v>
+      </c>
+      <c r="D5">
+        <v>1801.193548387097</v>
+      </c>
+      <c r="E5">
+        <v>1906</v>
+      </c>
+      <c r="F5">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>2023</v>
+      </c>
+      <c r="B6" t="s">
+        <v>635</v>
+      </c>
+      <c r="C6">
+        <v>1841.5</v>
+      </c>
+      <c r="D6">
+        <v>1830.433333333334</v>
+      </c>
+      <c r="E6">
+        <v>1899</v>
+      </c>
+      <c r="F6">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>2023</v>
+      </c>
+      <c r="B7" t="s">
+        <v>636</v>
+      </c>
+      <c r="C7">
+        <v>1767</v>
+      </c>
+      <c r="D7">
+        <v>1770.290322580645</v>
+      </c>
+      <c r="E7">
+        <v>1867</v>
+      </c>
+      <c r="F7">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>2023</v>
+      </c>
+      <c r="B8" t="s">
+        <v>637</v>
+      </c>
+      <c r="C8">
+        <v>1785</v>
+      </c>
+      <c r="D8">
+        <v>1789.033333333333</v>
+      </c>
+      <c r="E8">
+        <v>1872</v>
+      </c>
+      <c r="F8">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>2023</v>
+      </c>
+      <c r="B9" t="s">
+        <v>638</v>
+      </c>
+      <c r="C9">
+        <v>1782</v>
+      </c>
+      <c r="D9">
+        <v>1805.612903225806</v>
+      </c>
+      <c r="E9">
+        <v>1907</v>
+      </c>
+      <c r="F9">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>2024</v>
+      </c>
+      <c r="B10" t="s">
+        <v>639</v>
+      </c>
+      <c r="C10">
+        <v>1708</v>
+      </c>
+      <c r="D10">
+        <v>1749.709677419355</v>
+      </c>
+      <c r="E10">
+        <v>1867</v>
+      </c>
+      <c r="F10">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>2024</v>
+      </c>
+      <c r="B11" t="s">
+        <v>640</v>
+      </c>
+      <c r="C11">
+        <v>1827.5</v>
+      </c>
+      <c r="D11">
+        <v>1870.615384615384</v>
+      </c>
+      <c r="E11">
+        <v>2362</v>
+      </c>
+      <c r="F11">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>2024</v>
+      </c>
+      <c r="B12" t="s">
+        <v>641</v>
+      </c>
+      <c r="C12">
+        <v>2279</v>
+      </c>
+      <c r="D12">
+        <v>2242.774193548387</v>
+      </c>
+      <c r="E12">
+        <v>2602</v>
+      </c>
+      <c r="F12">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>2024</v>
+      </c>
+      <c r="B13" t="s">
+        <v>642</v>
+      </c>
+      <c r="C13">
+        <v>2011.5</v>
+      </c>
+      <c r="D13">
+        <v>1981.066666666666</v>
+      </c>
+      <c r="E13">
+        <v>2224</v>
+      </c>
+      <c r="F13">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>2024</v>
+      </c>
+      <c r="B14" t="s">
         <v>631</v>
       </c>
-      <c r="B4">
-        <v>1798</v>
-      </c>
-      <c r="C4">
-        <v>1783.870967741935</v>
-      </c>
-      <c r="D4">
-        <v>1885</v>
-      </c>
-      <c r="E4">
-        <v>1688</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
+      <c r="C14">
+        <v>2315</v>
+      </c>
+      <c r="D14">
+        <v>2303.193548387097</v>
+      </c>
+      <c r="E14">
+        <v>2382</v>
+      </c>
+      <c r="F14">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>2024</v>
+      </c>
+      <c r="B15" t="s">
         <v>632</v>
       </c>
-      <c r="B5">
-        <v>1810</v>
-      </c>
-      <c r="C5">
-        <v>1801.193548387097</v>
-      </c>
-      <c r="D5">
-        <v>1906</v>
-      </c>
-      <c r="E5">
-        <v>1742</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
+      <c r="C15">
+        <v>2111</v>
+      </c>
+      <c r="D15">
+        <v>2166.724137931034</v>
+      </c>
+      <c r="E15">
+        <v>2374</v>
+      </c>
+      <c r="F15">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="s">
         <v>633</v>
       </c>
-      <c r="B6">
-        <v>1841.5</v>
-      </c>
-      <c r="C6">
-        <v>1830.433333333334</v>
-      </c>
-      <c r="D6">
-        <v>1899</v>
-      </c>
-      <c r="E6">
-        <v>1743</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
+      <c r="C16">
+        <v>2068</v>
+      </c>
+      <c r="D16">
+        <v>2066.354838709678</v>
+      </c>
+      <c r="E16">
+        <v>2136</v>
+      </c>
+      <c r="F16">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>2024</v>
+      </c>
+      <c r="B17" t="s">
         <v>634</v>
       </c>
-      <c r="B7">
-        <v>1767</v>
-      </c>
-      <c r="C7">
-        <v>1770.290322580645</v>
-      </c>
-      <c r="D7">
-        <v>1867</v>
-      </c>
-      <c r="E7">
-        <v>1671</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
+      <c r="C17">
+        <v>2109</v>
+      </c>
+      <c r="D17">
+        <v>2106.857142857143</v>
+      </c>
+      <c r="E17">
+        <v>2159</v>
+      </c>
+      <c r="F17">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>2024</v>
+      </c>
+      <c r="B18" t="s">
         <v>635</v>
       </c>
-      <c r="B8">
-        <v>1785</v>
-      </c>
-      <c r="C8">
-        <v>1789.033333333333</v>
-      </c>
-      <c r="D8">
-        <v>1872</v>
-      </c>
-      <c r="E8">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
+      <c r="C18">
+        <v>2031.5</v>
+      </c>
+      <c r="D18">
+        <v>2039.214285714286</v>
+      </c>
+      <c r="E18">
+        <v>2103</v>
+      </c>
+      <c r="F18">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>2024</v>
+      </c>
+      <c r="B19" t="s">
         <v>636</v>
       </c>
-      <c r="B9">
-        <v>1782</v>
-      </c>
-      <c r="C9">
-        <v>1805.612903225806</v>
-      </c>
-      <c r="D9">
-        <v>1907</v>
-      </c>
-      <c r="E9">
-        <v>1683</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
+      <c r="C19">
+        <v>2040</v>
+      </c>
+      <c r="D19">
+        <v>2041.777777777778</v>
+      </c>
+      <c r="E19">
+        <v>2121</v>
+      </c>
+      <c r="F19">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>2024</v>
+      </c>
+      <c r="B20" t="s">
         <v>637</v>
       </c>
-      <c r="B10">
-        <v>1708</v>
-      </c>
-      <c r="C10">
-        <v>1749.709677419355</v>
-      </c>
-      <c r="D10">
-        <v>1867</v>
-      </c>
-      <c r="E10">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
+      <c r="C20">
+        <v>1822</v>
+      </c>
+      <c r="D20">
+        <v>1825.296296296296</v>
+      </c>
+      <c r="E20">
+        <v>1982</v>
+      </c>
+      <c r="F20">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>2024</v>
+      </c>
+      <c r="B21" t="s">
         <v>638</v>
       </c>
-      <c r="B11">
-        <v>1827.5</v>
-      </c>
-      <c r="C11">
-        <v>1870.615384615384</v>
-      </c>
-      <c r="D11">
-        <v>2362</v>
-      </c>
-      <c r="E11">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
+      <c r="C21">
+        <v>1893</v>
+      </c>
+      <c r="D21">
+        <v>1889.516129032258</v>
+      </c>
+      <c r="E21">
+        <v>1975</v>
+      </c>
+      <c r="F21">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>2025</v>
+      </c>
+      <c r="B22" t="s">
         <v>639</v>
       </c>
-      <c r="B12">
-        <v>2279</v>
-      </c>
-      <c r="C12">
-        <v>2242.774193548387</v>
-      </c>
-      <c r="D12">
-        <v>2602</v>
-      </c>
-      <c r="E12">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
+      <c r="C22">
+        <v>1673</v>
+      </c>
+      <c r="D22">
+        <v>1681.032258064516</v>
+      </c>
+      <c r="E22">
+        <v>1807</v>
+      </c>
+      <c r="F22">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>2025</v>
+      </c>
+      <c r="B23" t="s">
         <v>640</v>
       </c>
-      <c r="B13">
-        <v>2011.5</v>
-      </c>
-      <c r="C13">
-        <v>1981.066666666666</v>
-      </c>
-      <c r="D13">
-        <v>2224</v>
-      </c>
-      <c r="E13">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>641</v>
-      </c>
-      <c r="B14">
-        <v>2315</v>
-      </c>
-      <c r="C14">
-        <v>2303.193548387097</v>
-      </c>
-      <c r="D14">
-        <v>2382</v>
-      </c>
-      <c r="E14">
-        <v>2215</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>642</v>
-      </c>
-      <c r="B15">
-        <v>2111</v>
-      </c>
-      <c r="C15">
-        <v>2166.724137931034</v>
-      </c>
-      <c r="D15">
-        <v>2374</v>
-      </c>
-      <c r="E15">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>643</v>
-      </c>
-      <c r="B16">
-        <v>2068</v>
-      </c>
-      <c r="C16">
-        <v>2066.354838709678</v>
-      </c>
-      <c r="D16">
-        <v>2136</v>
-      </c>
-      <c r="E16">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>644</v>
-      </c>
-      <c r="B17">
-        <v>2109</v>
-      </c>
-      <c r="C17">
-        <v>2106.857142857143</v>
-      </c>
-      <c r="D17">
-        <v>2159</v>
-      </c>
-      <c r="E17">
-        <v>2057</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>645</v>
-      </c>
-      <c r="B18">
-        <v>2031.5</v>
-      </c>
-      <c r="C18">
-        <v>2039.214285714286</v>
-      </c>
-      <c r="D18">
-        <v>2103</v>
-      </c>
-      <c r="E18">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>646</v>
-      </c>
-      <c r="B19">
-        <v>2040</v>
-      </c>
-      <c r="C19">
-        <v>2041.777777777778</v>
-      </c>
-      <c r="D19">
-        <v>2121</v>
-      </c>
-      <c r="E19">
-        <v>1987</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>647</v>
-      </c>
-      <c r="B20">
-        <v>1822</v>
-      </c>
-      <c r="C20">
-        <v>1825.296296296296</v>
-      </c>
-      <c r="D20">
-        <v>1982</v>
-      </c>
-      <c r="E20">
-        <v>1619</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>648</v>
-      </c>
-      <c r="B21">
-        <v>1893</v>
-      </c>
-      <c r="C21">
-        <v>1889.516129032258</v>
-      </c>
-      <c r="D21">
-        <v>1975</v>
-      </c>
-      <c r="E21">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>649</v>
-      </c>
-      <c r="B22">
-        <v>1673</v>
-      </c>
-      <c r="C22">
-        <v>1681.032258064516</v>
-      </c>
-      <c r="D22">
-        <v>1807</v>
-      </c>
-      <c r="E22">
-        <v>1553</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>650</v>
-      </c>
-      <c r="B23">
+      <c r="C23">
         <v>1951</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>1939.157894736842</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>2080</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>1733</v>
       </c>
     </row>
@@ -7792,40 +7837,46 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>650</v>
-      </c>
-      <c r="B2">
+        <v>629</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C2">
         <v>192</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>189.2</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>200</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>171</v>
       </c>
     </row>
@@ -7894,40 +7945,46 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>650</v>
-      </c>
-      <c r="B2">
+        <v>629</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C2">
         <v>188</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>190.8</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>206</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>185</v>
       </c>
     </row>
@@ -7996,40 +8053,46 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>650</v>
-      </c>
-      <c r="B2">
+        <v>629</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C2">
         <v>30</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>29.4</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>30</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>28</v>
       </c>
     </row>

--- a/vag-rad/vag-rad_stats.xlsx
+++ b/vag-rad/vag-rad_stats.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="652">
   <si>
     <t>date</t>
   </si>
@@ -1917,6 +1917,12 @@
   </si>
   <si>
     <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
   </si>
   <si>
     <t>year</t>
@@ -2328,7 +2334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B631"/>
+  <dimension ref="A1:B633"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7377,6 +7383,22 @@
       </c>
       <c r="B631">
         <v>1942</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632" t="s">
+        <v>632</v>
+      </c>
+      <c r="B632">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633" t="s">
+        <v>633</v>
+      </c>
+      <c r="B633">
+        <v>1882</v>
       </c>
     </row>
   </sheetData>
@@ -7391,22 +7413,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7414,7 +7436,7 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C2">
         <v>1793</v>
@@ -7434,7 +7456,7 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C3">
         <v>1713.5</v>
@@ -7454,7 +7476,7 @@
         <v>2023</v>
       </c>
       <c r="B4" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C4">
         <v>1798</v>
@@ -7474,7 +7496,7 @@
         <v>2023</v>
       </c>
       <c r="B5" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C5">
         <v>1810</v>
@@ -7494,7 +7516,7 @@
         <v>2023</v>
       </c>
       <c r="B6" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C6">
         <v>1841.5</v>
@@ -7514,7 +7536,7 @@
         <v>2023</v>
       </c>
       <c r="B7" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C7">
         <v>1767</v>
@@ -7534,7 +7556,7 @@
         <v>2023</v>
       </c>
       <c r="B8" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C8">
         <v>1785</v>
@@ -7554,7 +7576,7 @@
         <v>2023</v>
       </c>
       <c r="B9" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C9">
         <v>1782</v>
@@ -7574,7 +7596,7 @@
         <v>2024</v>
       </c>
       <c r="B10" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C10">
         <v>1708</v>
@@ -7594,7 +7616,7 @@
         <v>2024</v>
       </c>
       <c r="B11" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C11">
         <v>1827.5</v>
@@ -7614,7 +7636,7 @@
         <v>2024</v>
       </c>
       <c r="B12" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C12">
         <v>2279</v>
@@ -7634,7 +7656,7 @@
         <v>2024</v>
       </c>
       <c r="B13" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C13">
         <v>2011.5</v>
@@ -7654,7 +7676,7 @@
         <v>2024</v>
       </c>
       <c r="B14" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C14">
         <v>2315</v>
@@ -7674,7 +7696,7 @@
         <v>2024</v>
       </c>
       <c r="B15" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C15">
         <v>2111</v>
@@ -7694,7 +7716,7 @@
         <v>2024</v>
       </c>
       <c r="B16" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C16">
         <v>2068</v>
@@ -7714,7 +7736,7 @@
         <v>2024</v>
       </c>
       <c r="B17" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C17">
         <v>2109</v>
@@ -7734,7 +7756,7 @@
         <v>2024</v>
       </c>
       <c r="B18" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C18">
         <v>2031.5</v>
@@ -7754,7 +7776,7 @@
         <v>2024</v>
       </c>
       <c r="B19" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C19">
         <v>2040</v>
@@ -7774,7 +7796,7 @@
         <v>2024</v>
       </c>
       <c r="B20" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C20">
         <v>1822</v>
@@ -7794,7 +7816,7 @@
         <v>2024</v>
       </c>
       <c r="B21" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C21">
         <v>1893</v>
@@ -7814,7 +7836,7 @@
         <v>2025</v>
       </c>
       <c r="B22" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C22">
         <v>1673</v>
@@ -7834,13 +7856,13 @@
         <v>2025</v>
       </c>
       <c r="B23" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C23">
-        <v>1971.5</v>
+        <v>1963</v>
       </c>
       <c r="D23">
-        <v>1964.653846153846</v>
+        <v>1959</v>
       </c>
       <c r="E23">
         <v>2086</v>
@@ -7856,7 +7878,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7961,6 +7983,22 @@
       </c>
       <c r="B13">
         <v>219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>632</v>
+      </c>
+      <c r="B14">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>633</v>
+      </c>
+      <c r="B15">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -7975,22 +8013,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7998,13 +8036,13 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C2">
         <v>193</v>
       </c>
       <c r="D2">
-        <v>192.4166666666666</v>
+        <v>192.1428571428572</v>
       </c>
       <c r="E2">
         <v>219</v>
@@ -8020,7 +8058,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8125,6 +8163,22 @@
       </c>
       <c r="B13">
         <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>632</v>
+      </c>
+      <c r="B14">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>633</v>
+      </c>
+      <c r="B15">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -8139,22 +8193,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8162,16 +8216,16 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C2">
-        <v>186</v>
+        <v>187.5</v>
       </c>
       <c r="D2">
-        <v>195.4166666666666</v>
+        <v>211.5</v>
       </c>
       <c r="E2">
-        <v>246</v>
+        <v>313</v>
       </c>
       <c r="F2">
         <v>175</v>
@@ -8184,7 +8238,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8289,6 +8343,22 @@
       </c>
       <c r="B13">
         <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>632</v>
+      </c>
+      <c r="B14">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>633</v>
+      </c>
+      <c r="B15">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -8303,22 +8373,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8326,13 +8396,13 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C2">
         <v>30</v>
       </c>
       <c r="D2">
-        <v>38.75</v>
+        <v>42.35714285714285</v>
       </c>
       <c r="E2">
         <v>68</v>

--- a/vag-rad/vag-rad_stats.xlsx
+++ b/vag-rad/vag-rad_stats.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="655">
   <si>
     <t>date</t>
   </si>
@@ -1923,6 +1923,15 @@
   </si>
   <si>
     <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>2025-03-01</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
   </si>
   <si>
     <t>year</t>
@@ -2334,7 +2343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B633"/>
+  <dimension ref="A1:B636"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7399,6 +7408,30 @@
       </c>
       <c r="B633">
         <v>1882</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634" t="s">
+        <v>634</v>
+      </c>
+      <c r="B634">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635" t="s">
+        <v>635</v>
+      </c>
+      <c r="B635">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636" t="s">
+        <v>636</v>
+      </c>
+      <c r="B636">
+        <v>1888</v>
       </c>
     </row>
   </sheetData>
@@ -7408,27 +7441,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7436,7 +7469,7 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C2">
         <v>1793</v>
@@ -7456,7 +7489,7 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C3">
         <v>1713.5</v>
@@ -7476,7 +7509,7 @@
         <v>2023</v>
       </c>
       <c r="B4" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C4">
         <v>1798</v>
@@ -7496,7 +7529,7 @@
         <v>2023</v>
       </c>
       <c r="B5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C5">
         <v>1810</v>
@@ -7516,7 +7549,7 @@
         <v>2023</v>
       </c>
       <c r="B6" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C6">
         <v>1841.5</v>
@@ -7536,7 +7569,7 @@
         <v>2023</v>
       </c>
       <c r="B7" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C7">
         <v>1767</v>
@@ -7556,7 +7589,7 @@
         <v>2023</v>
       </c>
       <c r="B8" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C8">
         <v>1785</v>
@@ -7576,7 +7609,7 @@
         <v>2023</v>
       </c>
       <c r="B9" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C9">
         <v>1782</v>
@@ -7596,7 +7629,7 @@
         <v>2024</v>
       </c>
       <c r="B10" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C10">
         <v>1708</v>
@@ -7616,7 +7649,7 @@
         <v>2024</v>
       </c>
       <c r="B11" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C11">
         <v>1827.5</v>
@@ -7636,7 +7669,7 @@
         <v>2024</v>
       </c>
       <c r="B12" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C12">
         <v>2279</v>
@@ -7656,7 +7689,7 @@
         <v>2024</v>
       </c>
       <c r="B13" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C13">
         <v>2011.5</v>
@@ -7676,7 +7709,7 @@
         <v>2024</v>
       </c>
       <c r="B14" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C14">
         <v>2315</v>
@@ -7696,7 +7729,7 @@
         <v>2024</v>
       </c>
       <c r="B15" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C15">
         <v>2111</v>
@@ -7716,7 +7749,7 @@
         <v>2024</v>
       </c>
       <c r="B16" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C16">
         <v>2068</v>
@@ -7736,7 +7769,7 @@
         <v>2024</v>
       </c>
       <c r="B17" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C17">
         <v>2109</v>
@@ -7756,7 +7789,7 @@
         <v>2024</v>
       </c>
       <c r="B18" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C18">
         <v>2031.5</v>
@@ -7776,7 +7809,7 @@
         <v>2024</v>
       </c>
       <c r="B19" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C19">
         <v>2040</v>
@@ -7796,7 +7829,7 @@
         <v>2024</v>
       </c>
       <c r="B20" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C20">
         <v>1822</v>
@@ -7816,7 +7849,7 @@
         <v>2024</v>
       </c>
       <c r="B21" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C21">
         <v>1893</v>
@@ -7836,7 +7869,7 @@
         <v>2025</v>
       </c>
       <c r="B22" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C22">
         <v>1673</v>
@@ -7856,7 +7889,7 @@
         <v>2025</v>
       </c>
       <c r="B23" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C23">
         <v>1963</v>
@@ -7869,6 +7902,26 @@
       </c>
       <c r="F23">
         <v>1733</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>2025</v>
+      </c>
+      <c r="B24" t="s">
+        <v>653</v>
+      </c>
+      <c r="C24">
+        <v>1888</v>
+      </c>
+      <c r="D24">
+        <v>1888.333333333333</v>
+      </c>
+      <c r="E24">
+        <v>1895</v>
+      </c>
+      <c r="F24">
+        <v>1882</v>
       </c>
     </row>
   </sheetData>
@@ -7878,7 +7931,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7999,6 +8052,30 @@
       </c>
       <c r="B15">
         <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>634</v>
+      </c>
+      <c r="B16">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>635</v>
+      </c>
+      <c r="B17">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>636</v>
+      </c>
+      <c r="B18">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -8008,27 +8085,27 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8036,7 +8113,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C2">
         <v>193</v>
@@ -8049,6 +8126,26 @@
       </c>
       <c r="F2">
         <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C3">
+        <v>206</v>
+      </c>
+      <c r="D3">
+        <v>206</v>
+      </c>
+      <c r="E3">
+        <v>211</v>
+      </c>
+      <c r="F3">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -8058,7 +8155,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8179,6 +8276,30 @@
       </c>
       <c r="B15">
         <v>303</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>634</v>
+      </c>
+      <c r="B16">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>635</v>
+      </c>
+      <c r="B17">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>636</v>
+      </c>
+      <c r="B18">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -8188,27 +8309,27 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8216,7 +8337,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C2">
         <v>187.5</v>
@@ -8229,6 +8350,26 @@
       </c>
       <c r="F2">
         <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C3">
+        <v>301</v>
+      </c>
+      <c r="D3">
+        <v>301</v>
+      </c>
+      <c r="E3">
+        <v>302</v>
+      </c>
+      <c r="F3">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -8238,7 +8379,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8359,6 +8500,30 @@
       </c>
       <c r="B15">
         <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>634</v>
+      </c>
+      <c r="B16">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>635</v>
+      </c>
+      <c r="B17">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>636</v>
+      </c>
+      <c r="B18">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -8368,27 +8533,27 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8396,7 +8561,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -8409,6 +8574,26 @@
       </c>
       <c r="F2">
         <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C3">
+        <v>63</v>
+      </c>
+      <c r="D3">
+        <v>64</v>
+      </c>
+      <c r="E3">
+        <v>66</v>
+      </c>
+      <c r="F3">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/vag-rad/vag-rad_stats.xlsx
+++ b/vag-rad/vag-rad_stats.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="656">
   <si>
     <t>date</t>
   </si>
@@ -1932,6 +1932,9 @@
   </si>
   <si>
     <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>2025-03-04</t>
   </si>
   <si>
     <t>year</t>
@@ -2343,7 +2346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B636"/>
+  <dimension ref="A1:B637"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7432,6 +7435,14 @@
       </c>
       <c r="B636">
         <v>1888</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637" t="s">
+        <v>637</v>
+      </c>
+      <c r="B637">
+        <v>1891</v>
       </c>
     </row>
   </sheetData>
@@ -7446,22 +7457,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7469,7 +7480,7 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C2">
         <v>1793</v>
@@ -7489,7 +7500,7 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C3">
         <v>1713.5</v>
@@ -7509,7 +7520,7 @@
         <v>2023</v>
       </c>
       <c r="B4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C4">
         <v>1798</v>
@@ -7529,7 +7540,7 @@
         <v>2023</v>
       </c>
       <c r="B5" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C5">
         <v>1810</v>
@@ -7549,7 +7560,7 @@
         <v>2023</v>
       </c>
       <c r="B6" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C6">
         <v>1841.5</v>
@@ -7569,7 +7580,7 @@
         <v>2023</v>
       </c>
       <c r="B7" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C7">
         <v>1767</v>
@@ -7589,7 +7600,7 @@
         <v>2023</v>
       </c>
       <c r="B8" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C8">
         <v>1785</v>
@@ -7609,7 +7620,7 @@
         <v>2023</v>
       </c>
       <c r="B9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C9">
         <v>1782</v>
@@ -7629,7 +7640,7 @@
         <v>2024</v>
       </c>
       <c r="B10" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C10">
         <v>1708</v>
@@ -7649,7 +7660,7 @@
         <v>2024</v>
       </c>
       <c r="B11" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C11">
         <v>1827.5</v>
@@ -7669,7 +7680,7 @@
         <v>2024</v>
       </c>
       <c r="B12" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C12">
         <v>2279</v>
@@ -7689,7 +7700,7 @@
         <v>2024</v>
       </c>
       <c r="B13" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C13">
         <v>2011.5</v>
@@ -7709,7 +7720,7 @@
         <v>2024</v>
       </c>
       <c r="B14" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C14">
         <v>2315</v>
@@ -7729,7 +7740,7 @@
         <v>2024</v>
       </c>
       <c r="B15" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C15">
         <v>2111</v>
@@ -7749,7 +7760,7 @@
         <v>2024</v>
       </c>
       <c r="B16" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C16">
         <v>2068</v>
@@ -7769,7 +7780,7 @@
         <v>2024</v>
       </c>
       <c r="B17" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C17">
         <v>2109</v>
@@ -7789,7 +7800,7 @@
         <v>2024</v>
       </c>
       <c r="B18" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C18">
         <v>2031.5</v>
@@ -7809,7 +7820,7 @@
         <v>2024</v>
       </c>
       <c r="B19" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C19">
         <v>2040</v>
@@ -7829,7 +7840,7 @@
         <v>2024</v>
       </c>
       <c r="B20" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C20">
         <v>1822</v>
@@ -7849,7 +7860,7 @@
         <v>2024</v>
       </c>
       <c r="B21" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C21">
         <v>1893</v>
@@ -7869,7 +7880,7 @@
         <v>2025</v>
       </c>
       <c r="B22" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C22">
         <v>1673</v>
@@ -7889,7 +7900,7 @@
         <v>2025</v>
       </c>
       <c r="B23" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C23">
         <v>1963</v>
@@ -7909,13 +7920,13 @@
         <v>2025</v>
       </c>
       <c r="B24" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C24">
-        <v>1888</v>
+        <v>1889.5</v>
       </c>
       <c r="D24">
-        <v>1888.333333333333</v>
+        <v>1889</v>
       </c>
       <c r="E24">
         <v>1895</v>
@@ -7931,7 +7942,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8076,6 +8087,14 @@
       </c>
       <c r="B18">
         <v>211</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>637</v>
+      </c>
+      <c r="B19">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -8090,22 +8109,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8113,7 +8132,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C2">
         <v>193</v>
@@ -8133,16 +8152,16 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C3">
-        <v>206</v>
+        <v>208.5</v>
       </c>
       <c r="D3">
-        <v>206</v>
+        <v>208.25</v>
       </c>
       <c r="E3">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F3">
         <v>201</v>
@@ -8155,7 +8174,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8300,6 +8319,14 @@
       </c>
       <c r="B18">
         <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>637</v>
+      </c>
+      <c r="B19">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -8314,22 +8341,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8337,7 +8364,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C2">
         <v>187.5</v>
@@ -8357,7 +8384,7 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C3">
         <v>301</v>
@@ -8379,7 +8406,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8524,6 +8551,14 @@
       </c>
       <c r="B18">
         <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>637</v>
+      </c>
+      <c r="B19">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -8538,22 +8573,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8561,7 +8596,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -8581,19 +8616,19 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C3">
         <v>63</v>
       </c>
       <c r="D3">
-        <v>64</v>
+        <v>63.5</v>
       </c>
       <c r="E3">
         <v>66</v>
       </c>
       <c r="F3">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/vag-rad/vag-rad_stats.xlsx
+++ b/vag-rad/vag-rad_stats.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="671">
   <si>
     <t>date</t>
   </si>
@@ -1935,6 +1935,51 @@
   </si>
   <si>
     <t>2025-03-04</t>
+  </si>
+  <si>
+    <t>2025-03-05</t>
+  </si>
+  <si>
+    <t>2025-03-06</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>2025-03-09</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>2025-03-11</t>
+  </si>
+  <si>
+    <t>2025-03-12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>2025-03-14</t>
+  </si>
+  <si>
+    <t>2025-03-15</t>
+  </si>
+  <si>
+    <t>2025-03-16</t>
+  </si>
+  <si>
+    <t>2025-03-17</t>
+  </si>
+  <si>
+    <t>2025-03-18</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
   </si>
   <si>
     <t>year</t>
@@ -2346,7 +2391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B637"/>
+  <dimension ref="A1:B652"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7443,6 +7488,126 @@
       </c>
       <c r="B637">
         <v>1891</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638" t="s">
+        <v>638</v>
+      </c>
+      <c r="B638">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639" t="s">
+        <v>639</v>
+      </c>
+      <c r="B639">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640" t="s">
+        <v>640</v>
+      </c>
+      <c r="B640">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641" t="s">
+        <v>641</v>
+      </c>
+      <c r="B641">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642" t="s">
+        <v>642</v>
+      </c>
+      <c r="B642">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643" t="s">
+        <v>643</v>
+      </c>
+      <c r="B643">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644" t="s">
+        <v>644</v>
+      </c>
+      <c r="B644">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645" t="s">
+        <v>645</v>
+      </c>
+      <c r="B645">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646" t="s">
+        <v>646</v>
+      </c>
+      <c r="B646">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647" t="s">
+        <v>647</v>
+      </c>
+      <c r="B647">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648" t="s">
+        <v>648</v>
+      </c>
+      <c r="B648">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649" t="s">
+        <v>649</v>
+      </c>
+      <c r="B649">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650" t="s">
+        <v>650</v>
+      </c>
+      <c r="B650">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651" t="s">
+        <v>651</v>
+      </c>
+      <c r="B651">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652" t="s">
+        <v>652</v>
+      </c>
+      <c r="B652">
+        <v>1805</v>
       </c>
     </row>
   </sheetData>
@@ -7457,22 +7622,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>639</v>
+        <v>654</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>642</v>
+        <v>657</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7480,7 +7645,7 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="C2">
         <v>1793</v>
@@ -7500,7 +7665,7 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>645</v>
+        <v>660</v>
       </c>
       <c r="C3">
         <v>1713.5</v>
@@ -7520,7 +7685,7 @@
         <v>2023</v>
       </c>
       <c r="B4" t="s">
-        <v>646</v>
+        <v>661</v>
       </c>
       <c r="C4">
         <v>1798</v>
@@ -7540,7 +7705,7 @@
         <v>2023</v>
       </c>
       <c r="B5" t="s">
-        <v>647</v>
+        <v>662</v>
       </c>
       <c r="C5">
         <v>1810</v>
@@ -7560,7 +7725,7 @@
         <v>2023</v>
       </c>
       <c r="B6" t="s">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="C6">
         <v>1841.5</v>
@@ -7580,7 +7745,7 @@
         <v>2023</v>
       </c>
       <c r="B7" t="s">
-        <v>649</v>
+        <v>664</v>
       </c>
       <c r="C7">
         <v>1767</v>
@@ -7600,7 +7765,7 @@
         <v>2023</v>
       </c>
       <c r="B8" t="s">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="C8">
         <v>1785</v>
@@ -7620,7 +7785,7 @@
         <v>2023</v>
       </c>
       <c r="B9" t="s">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="C9">
         <v>1782</v>
@@ -7640,7 +7805,7 @@
         <v>2024</v>
       </c>
       <c r="B10" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="C10">
         <v>1708</v>
@@ -7660,7 +7825,7 @@
         <v>2024</v>
       </c>
       <c r="B11" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="C11">
         <v>1827.5</v>
@@ -7680,7 +7845,7 @@
         <v>2024</v>
       </c>
       <c r="B12" t="s">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="C12">
         <v>2279</v>
@@ -7700,7 +7865,7 @@
         <v>2024</v>
       </c>
       <c r="B13" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
       <c r="C13">
         <v>2011.5</v>
@@ -7720,7 +7885,7 @@
         <v>2024</v>
       </c>
       <c r="B14" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="C14">
         <v>2315</v>
@@ -7740,7 +7905,7 @@
         <v>2024</v>
       </c>
       <c r="B15" t="s">
-        <v>645</v>
+        <v>660</v>
       </c>
       <c r="C15">
         <v>2111</v>
@@ -7760,7 +7925,7 @@
         <v>2024</v>
       </c>
       <c r="B16" t="s">
-        <v>646</v>
+        <v>661</v>
       </c>
       <c r="C16">
         <v>2068</v>
@@ -7780,7 +7945,7 @@
         <v>2024</v>
       </c>
       <c r="B17" t="s">
-        <v>647</v>
+        <v>662</v>
       </c>
       <c r="C17">
         <v>2109</v>
@@ -7800,7 +7965,7 @@
         <v>2024</v>
       </c>
       <c r="B18" t="s">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="C18">
         <v>2031.5</v>
@@ -7820,7 +7985,7 @@
         <v>2024</v>
       </c>
       <c r="B19" t="s">
-        <v>649</v>
+        <v>664</v>
       </c>
       <c r="C19">
         <v>2040</v>
@@ -7840,7 +8005,7 @@
         <v>2024</v>
       </c>
       <c r="B20" t="s">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="C20">
         <v>1822</v>
@@ -7860,7 +8025,7 @@
         <v>2024</v>
       </c>
       <c r="B21" t="s">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="C21">
         <v>1893</v>
@@ -7880,7 +8045,7 @@
         <v>2025</v>
       </c>
       <c r="B22" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="C22">
         <v>1673</v>
@@ -7900,7 +8065,7 @@
         <v>2025</v>
       </c>
       <c r="B23" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="C23">
         <v>1963</v>
@@ -7920,19 +8085,19 @@
         <v>2025</v>
       </c>
       <c r="B24" t="s">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="C24">
-        <v>1889.5</v>
+        <v>1844</v>
       </c>
       <c r="D24">
-        <v>1889</v>
+        <v>1842.894736842105</v>
       </c>
       <c r="E24">
         <v>1895</v>
       </c>
       <c r="F24">
-        <v>1882</v>
+        <v>1786</v>
       </c>
     </row>
   </sheetData>
@@ -7942,7 +8107,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8095,6 +8260,126 @@
       </c>
       <c r="B19">
         <v>215</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>638</v>
+      </c>
+      <c r="B20">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>639</v>
+      </c>
+      <c r="B21">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>640</v>
+      </c>
+      <c r="B22">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>641</v>
+      </c>
+      <c r="B23">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>642</v>
+      </c>
+      <c r="B24">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>643</v>
+      </c>
+      <c r="B25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>644</v>
+      </c>
+      <c r="B26">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>645</v>
+      </c>
+      <c r="B27">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>646</v>
+      </c>
+      <c r="B28">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>647</v>
+      </c>
+      <c r="B29">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>648</v>
+      </c>
+      <c r="B30">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>649</v>
+      </c>
+      <c r="B31">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>650</v>
+      </c>
+      <c r="B32">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>651</v>
+      </c>
+      <c r="B33">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>652</v>
+      </c>
+      <c r="B34">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -8109,22 +8394,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>639</v>
+        <v>654</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>642</v>
+        <v>657</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8132,7 +8417,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="C2">
         <v>193</v>
@@ -8152,16 +8437,16 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="C3">
-        <v>208.5</v>
+        <v>230</v>
       </c>
       <c r="D3">
-        <v>208.25</v>
+        <v>235.8947368421053</v>
       </c>
       <c r="E3">
-        <v>215</v>
+        <v>285</v>
       </c>
       <c r="F3">
         <v>201</v>
@@ -8174,7 +8459,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8327,6 +8612,126 @@
       </c>
       <c r="B19">
         <v>301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>638</v>
+      </c>
+      <c r="B20">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>639</v>
+      </c>
+      <c r="B21">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>640</v>
+      </c>
+      <c r="B22">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>641</v>
+      </c>
+      <c r="B23">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>642</v>
+      </c>
+      <c r="B24">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>643</v>
+      </c>
+      <c r="B25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>644</v>
+      </c>
+      <c r="B26">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>645</v>
+      </c>
+      <c r="B27">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>646</v>
+      </c>
+      <c r="B28">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>647</v>
+      </c>
+      <c r="B29">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>648</v>
+      </c>
+      <c r="B30">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>649</v>
+      </c>
+      <c r="B31">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>650</v>
+      </c>
+      <c r="B32">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>651</v>
+      </c>
+      <c r="B33">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>652</v>
+      </c>
+      <c r="B34">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -8341,22 +8746,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>639</v>
+        <v>654</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>642</v>
+        <v>657</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8364,7 +8769,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="C2">
         <v>187.5</v>
@@ -8384,19 +8789,19 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="C3">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D3">
-        <v>301</v>
+        <v>299.6842105263158</v>
       </c>
       <c r="E3">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="F3">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -8406,7 +8811,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8559,6 +8964,126 @@
       </c>
       <c r="B19">
         <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>638</v>
+      </c>
+      <c r="B20">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>639</v>
+      </c>
+      <c r="B21">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>640</v>
+      </c>
+      <c r="B22">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>641</v>
+      </c>
+      <c r="B23">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>642</v>
+      </c>
+      <c r="B24">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>643</v>
+      </c>
+      <c r="B25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>644</v>
+      </c>
+      <c r="B26">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>645</v>
+      </c>
+      <c r="B27">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>646</v>
+      </c>
+      <c r="B28">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>647</v>
+      </c>
+      <c r="B29">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>648</v>
+      </c>
+      <c r="B30">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>649</v>
+      </c>
+      <c r="B31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>650</v>
+      </c>
+      <c r="B32">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>651</v>
+      </c>
+      <c r="B33">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>652</v>
+      </c>
+      <c r="B34">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -8573,22 +9098,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>639</v>
+        <v>654</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>642</v>
+        <v>657</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8596,7 +9121,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -8616,19 +9141,19 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3">
-        <v>63.5</v>
+        <v>62.21052631578947</v>
       </c>
       <c r="E3">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F3">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/vag-rad/vag-rad_stats.xlsx
+++ b/vag-rad/vag-rad_stats.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="678">
   <si>
     <t>date</t>
   </si>
@@ -1980,6 +1980,27 @@
   </si>
   <si>
     <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>2025-03-20</t>
+  </si>
+  <si>
+    <t>2025-03-21</t>
+  </si>
+  <si>
+    <t>2025-03-22</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>2025-03-24</t>
+  </si>
+  <si>
+    <t>2025-03-25</t>
+  </si>
+  <si>
+    <t>2025-03-26</t>
   </si>
   <si>
     <t>year</t>
@@ -2391,7 +2412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B652"/>
+  <dimension ref="A1:B659"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7608,6 +7629,62 @@
       </c>
       <c r="B652">
         <v>1805</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653" t="s">
+        <v>653</v>
+      </c>
+      <c r="B653">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654" t="s">
+        <v>654</v>
+      </c>
+      <c r="B654">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655" t="s">
+        <v>655</v>
+      </c>
+      <c r="B655">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656" t="s">
+        <v>656</v>
+      </c>
+      <c r="B656">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657" t="s">
+        <v>657</v>
+      </c>
+      <c r="B657">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658" t="s">
+        <v>658</v>
+      </c>
+      <c r="B658">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659" t="s">
+        <v>659</v>
+      </c>
+      <c r="B659">
+        <v>1786</v>
       </c>
     </row>
   </sheetData>
@@ -7622,22 +7699,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7645,7 +7722,7 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="C2">
         <v>1793</v>
@@ -7665,7 +7742,7 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="C3">
         <v>1713.5</v>
@@ -7685,7 +7762,7 @@
         <v>2023</v>
       </c>
       <c r="B4" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="C4">
         <v>1798</v>
@@ -7705,7 +7782,7 @@
         <v>2023</v>
       </c>
       <c r="B5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C5">
         <v>1810</v>
@@ -7725,7 +7802,7 @@
         <v>2023</v>
       </c>
       <c r="B6" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="C6">
         <v>1841.5</v>
@@ -7745,7 +7822,7 @@
         <v>2023</v>
       </c>
       <c r="B7" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="C7">
         <v>1767</v>
@@ -7765,7 +7842,7 @@
         <v>2023</v>
       </c>
       <c r="B8" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="C8">
         <v>1785</v>
@@ -7785,7 +7862,7 @@
         <v>2023</v>
       </c>
       <c r="B9" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="C9">
         <v>1782</v>
@@ -7805,7 +7882,7 @@
         <v>2024</v>
       </c>
       <c r="B10" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="C10">
         <v>1708</v>
@@ -7825,7 +7902,7 @@
         <v>2024</v>
       </c>
       <c r="B11" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="C11">
         <v>1827.5</v>
@@ -7845,7 +7922,7 @@
         <v>2024</v>
       </c>
       <c r="B12" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="C12">
         <v>2279</v>
@@ -7865,7 +7942,7 @@
         <v>2024</v>
       </c>
       <c r="B13" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="C13">
         <v>2011.5</v>
@@ -7885,7 +7962,7 @@
         <v>2024</v>
       </c>
       <c r="B14" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="C14">
         <v>2315</v>
@@ -7905,7 +7982,7 @@
         <v>2024</v>
       </c>
       <c r="B15" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="C15">
         <v>2111</v>
@@ -7925,7 +8002,7 @@
         <v>2024</v>
       </c>
       <c r="B16" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="C16">
         <v>2068</v>
@@ -7945,7 +8022,7 @@
         <v>2024</v>
       </c>
       <c r="B17" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C17">
         <v>2109</v>
@@ -7965,7 +8042,7 @@
         <v>2024</v>
       </c>
       <c r="B18" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="C18">
         <v>2031.5</v>
@@ -7985,7 +8062,7 @@
         <v>2024</v>
       </c>
       <c r="B19" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="C19">
         <v>2040</v>
@@ -8005,7 +8082,7 @@
         <v>2024</v>
       </c>
       <c r="B20" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="C20">
         <v>1822</v>
@@ -8025,7 +8102,7 @@
         <v>2024</v>
       </c>
       <c r="B21" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="C21">
         <v>1893</v>
@@ -8045,7 +8122,7 @@
         <v>2025</v>
       </c>
       <c r="B22" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="C22">
         <v>1673</v>
@@ -8065,7 +8142,7 @@
         <v>2025</v>
       </c>
       <c r="B23" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="C23">
         <v>1963</v>
@@ -8085,19 +8162,19 @@
         <v>2025</v>
       </c>
       <c r="B24" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="C24">
-        <v>1844</v>
+        <v>1820.5</v>
       </c>
       <c r="D24">
-        <v>1842.894736842105</v>
+        <v>1830.384615384616</v>
       </c>
       <c r="E24">
         <v>1895</v>
       </c>
       <c r="F24">
-        <v>1786</v>
+        <v>1774</v>
       </c>
     </row>
   </sheetData>
@@ -8107,7 +8184,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8380,6 +8457,62 @@
       </c>
       <c r="B34">
         <v>285</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>653</v>
+      </c>
+      <c r="B35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>654</v>
+      </c>
+      <c r="B36">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>655</v>
+      </c>
+      <c r="B37">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>656</v>
+      </c>
+      <c r="B38">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>657</v>
+      </c>
+      <c r="B39">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>658</v>
+      </c>
+      <c r="B40">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>659</v>
+      </c>
+      <c r="B41">
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -8394,22 +8527,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8417,7 +8550,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="C2">
         <v>193</v>
@@ -8437,16 +8570,16 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="C3">
-        <v>230</v>
+        <v>243.5</v>
       </c>
       <c r="D3">
-        <v>235.8947368421053</v>
+        <v>252.1923076923077</v>
       </c>
       <c r="E3">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="F3">
         <v>201</v>
@@ -8459,7 +8592,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8732,6 +8865,62 @@
       </c>
       <c r="B34">
         <v>294</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>653</v>
+      </c>
+      <c r="B35">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>654</v>
+      </c>
+      <c r="B36">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>655</v>
+      </c>
+      <c r="B37">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>656</v>
+      </c>
+      <c r="B38">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>657</v>
+      </c>
+      <c r="B39">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>658</v>
+      </c>
+      <c r="B40">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>659</v>
+      </c>
+      <c r="B41">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -8746,22 +8935,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8769,7 +8958,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="C2">
         <v>187.5</v>
@@ -8789,13 +8978,13 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="C3">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D3">
-        <v>299.6842105263158</v>
+        <v>299.8846153846154</v>
       </c>
       <c r="E3">
         <v>315</v>
@@ -8811,7 +9000,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -9084,6 +9273,62 @@
       </c>
       <c r="B34">
         <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>653</v>
+      </c>
+      <c r="B35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>654</v>
+      </c>
+      <c r="B36">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>655</v>
+      </c>
+      <c r="B37">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>656</v>
+      </c>
+      <c r="B38">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>657</v>
+      </c>
+      <c r="B39">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>658</v>
+      </c>
+      <c r="B40">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>659</v>
+      </c>
+      <c r="B41">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -9098,22 +9343,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9121,7 +9366,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -9141,13 +9386,13 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="C3">
-        <v>62</v>
+        <v>61.5</v>
       </c>
       <c r="D3">
-        <v>62.21052631578947</v>
+        <v>61.92307692307692</v>
       </c>
       <c r="E3">
         <v>73</v>

--- a/vag-rad/vag-rad_stats.xlsx
+++ b/vag-rad/vag-rad_stats.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="681">
   <si>
     <t>date</t>
   </si>
@@ -2001,6 +2001,15 @@
   </si>
   <si>
     <t>2025-03-26</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>2025-03-29</t>
   </si>
   <si>
     <t>year</t>
@@ -2412,7 +2421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B659"/>
+  <dimension ref="A1:B662"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7685,6 +7694,30 @@
       </c>
       <c r="B659">
         <v>1786</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660" t="s">
+        <v>660</v>
+      </c>
+      <c r="B660">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661" t="s">
+        <v>661</v>
+      </c>
+      <c r="B661">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662" t="s">
+        <v>662</v>
+      </c>
+      <c r="B662">
+        <v>1824</v>
       </c>
     </row>
   </sheetData>
@@ -7699,22 +7732,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7722,7 +7755,7 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C2">
         <v>1793</v>
@@ -7742,7 +7775,7 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C3">
         <v>1713.5</v>
@@ -7762,7 +7795,7 @@
         <v>2023</v>
       </c>
       <c r="B4" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C4">
         <v>1798</v>
@@ -7782,7 +7815,7 @@
         <v>2023</v>
       </c>
       <c r="B5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C5">
         <v>1810</v>
@@ -7802,7 +7835,7 @@
         <v>2023</v>
       </c>
       <c r="B6" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C6">
         <v>1841.5</v>
@@ -7822,7 +7855,7 @@
         <v>2023</v>
       </c>
       <c r="B7" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C7">
         <v>1767</v>
@@ -7842,7 +7875,7 @@
         <v>2023</v>
       </c>
       <c r="B8" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C8">
         <v>1785</v>
@@ -7862,7 +7895,7 @@
         <v>2023</v>
       </c>
       <c r="B9" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C9">
         <v>1782</v>
@@ -7882,7 +7915,7 @@
         <v>2024</v>
       </c>
       <c r="B10" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C10">
         <v>1708</v>
@@ -7902,7 +7935,7 @@
         <v>2024</v>
       </c>
       <c r="B11" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C11">
         <v>1827.5</v>
@@ -7922,7 +7955,7 @@
         <v>2024</v>
       </c>
       <c r="B12" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C12">
         <v>2279</v>
@@ -7942,7 +7975,7 @@
         <v>2024</v>
       </c>
       <c r="B13" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C13">
         <v>2011.5</v>
@@ -7962,7 +7995,7 @@
         <v>2024</v>
       </c>
       <c r="B14" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C14">
         <v>2315</v>
@@ -7982,7 +8015,7 @@
         <v>2024</v>
       </c>
       <c r="B15" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C15">
         <v>2111</v>
@@ -8002,7 +8035,7 @@
         <v>2024</v>
       </c>
       <c r="B16" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C16">
         <v>2068</v>
@@ -8022,7 +8055,7 @@
         <v>2024</v>
       </c>
       <c r="B17" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C17">
         <v>2109</v>
@@ -8042,7 +8075,7 @@
         <v>2024</v>
       </c>
       <c r="B18" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C18">
         <v>2031.5</v>
@@ -8062,7 +8095,7 @@
         <v>2024</v>
       </c>
       <c r="B19" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C19">
         <v>2040</v>
@@ -8082,7 +8115,7 @@
         <v>2024</v>
       </c>
       <c r="B20" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C20">
         <v>1822</v>
@@ -8102,7 +8135,7 @@
         <v>2024</v>
       </c>
       <c r="B21" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C21">
         <v>1893</v>
@@ -8122,7 +8155,7 @@
         <v>2025</v>
       </c>
       <c r="B22" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C22">
         <v>1673</v>
@@ -8142,7 +8175,7 @@
         <v>2025</v>
       </c>
       <c r="B23" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C23">
         <v>1963</v>
@@ -8162,13 +8195,13 @@
         <v>2025</v>
       </c>
       <c r="B24" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C24">
-        <v>1820.5</v>
+        <v>1823</v>
       </c>
       <c r="D24">
-        <v>1830.384615384616</v>
+        <v>1831.068965517241</v>
       </c>
       <c r="E24">
         <v>1895</v>
@@ -8184,7 +8217,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8513,6 +8546,30 @@
       </c>
       <c r="B41">
         <v>304</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>660</v>
+      </c>
+      <c r="B42">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>661</v>
+      </c>
+      <c r="B43">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>662</v>
+      </c>
+      <c r="B44">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -8527,22 +8584,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8550,7 +8607,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C2">
         <v>193</v>
@@ -8570,13 +8627,13 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C3">
-        <v>243.5</v>
+        <v>261</v>
       </c>
       <c r="D3">
-        <v>252.1923076923077</v>
+        <v>253.7931034482759</v>
       </c>
       <c r="E3">
         <v>311</v>
@@ -8592,7 +8649,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8921,6 +8978,30 @@
       </c>
       <c r="B41">
         <v>301</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>660</v>
+      </c>
+      <c r="B42">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>661</v>
+      </c>
+      <c r="B43">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>662</v>
+      </c>
+      <c r="B44">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -8935,22 +9016,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8958,7 +9039,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C2">
         <v>187.5</v>
@@ -8978,13 +9059,13 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C3">
         <v>300</v>
       </c>
       <c r="D3">
-        <v>299.8846153846154</v>
+        <v>299.8275862068966</v>
       </c>
       <c r="E3">
         <v>315</v>
@@ -9000,7 +9081,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -9329,6 +9410,30 @@
       </c>
       <c r="B41">
         <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>660</v>
+      </c>
+      <c r="B42">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>661</v>
+      </c>
+      <c r="B43">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>662</v>
+      </c>
+      <c r="B44">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -9343,22 +9448,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9366,7 +9471,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -9386,13 +9491,13 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C3">
-        <v>61.5</v>
+        <v>61</v>
       </c>
       <c r="D3">
-        <v>61.92307692307692</v>
+        <v>61.68965517241379</v>
       </c>
       <c r="E3">
         <v>73</v>

--- a/vag-rad/vag-rad_stats.xlsx
+++ b/vag-rad/vag-rad_stats.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="699">
   <si>
     <t>date</t>
   </si>
@@ -2010,6 +2010,60 @@
   </si>
   <si>
     <t>2025-03-29</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>2025-03-31</t>
+  </si>
+  <si>
+    <t>2025-04-01</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>2025-04-05</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>2025-04-09</t>
+  </si>
+  <si>
+    <t>2025-04-10</t>
+  </si>
+  <si>
+    <t>2025-04-11</t>
+  </si>
+  <si>
+    <t>2025-04-12</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>2025-04-14</t>
+  </si>
+  <si>
+    <t>2025-04-15</t>
+  </si>
+  <si>
+    <t>2025-04-16</t>
   </si>
   <si>
     <t>year</t>
@@ -2421,7 +2475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B662"/>
+  <dimension ref="A1:B680"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7718,6 +7772,150 @@
       </c>
       <c r="B662">
         <v>1824</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663" t="s">
+        <v>663</v>
+      </c>
+      <c r="B663">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664" t="s">
+        <v>664</v>
+      </c>
+      <c r="B664">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665" t="s">
+        <v>665</v>
+      </c>
+      <c r="B665">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666" t="s">
+        <v>666</v>
+      </c>
+      <c r="B666">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667" t="s">
+        <v>667</v>
+      </c>
+      <c r="B667">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668" t="s">
+        <v>668</v>
+      </c>
+      <c r="B668">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669" t="s">
+        <v>669</v>
+      </c>
+      <c r="B669">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670" t="s">
+        <v>670</v>
+      </c>
+      <c r="B670">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671" t="s">
+        <v>671</v>
+      </c>
+      <c r="B671">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672" t="s">
+        <v>672</v>
+      </c>
+      <c r="B672">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673" t="s">
+        <v>673</v>
+      </c>
+      <c r="B673">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674" t="s">
+        <v>674</v>
+      </c>
+      <c r="B674">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675" t="s">
+        <v>675</v>
+      </c>
+      <c r="B675">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676" t="s">
+        <v>676</v>
+      </c>
+      <c r="B676">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677" t="s">
+        <v>677</v>
+      </c>
+      <c r="B677">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678" t="s">
+        <v>678</v>
+      </c>
+      <c r="B678">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679" t="s">
+        <v>679</v>
+      </c>
+      <c r="B679">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680" t="s">
+        <v>680</v>
+      </c>
+      <c r="B680">
+        <v>1743</v>
       </c>
     </row>
   </sheetData>
@@ -7727,27 +7925,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7755,7 +7953,7 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>669</v>
+        <v>687</v>
       </c>
       <c r="C2">
         <v>1793</v>
@@ -7775,7 +7973,7 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="C3">
         <v>1713.5</v>
@@ -7795,7 +7993,7 @@
         <v>2023</v>
       </c>
       <c r="B4" t="s">
-        <v>671</v>
+        <v>689</v>
       </c>
       <c r="C4">
         <v>1798</v>
@@ -7815,7 +8013,7 @@
         <v>2023</v>
       </c>
       <c r="B5" t="s">
-        <v>672</v>
+        <v>690</v>
       </c>
       <c r="C5">
         <v>1810</v>
@@ -7835,7 +8033,7 @@
         <v>2023</v>
       </c>
       <c r="B6" t="s">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="C6">
         <v>1841.5</v>
@@ -7855,7 +8053,7 @@
         <v>2023</v>
       </c>
       <c r="B7" t="s">
-        <v>674</v>
+        <v>692</v>
       </c>
       <c r="C7">
         <v>1767</v>
@@ -7875,7 +8073,7 @@
         <v>2023</v>
       </c>
       <c r="B8" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="C8">
         <v>1785</v>
@@ -7895,7 +8093,7 @@
         <v>2023</v>
       </c>
       <c r="B9" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="C9">
         <v>1782</v>
@@ -7915,7 +8113,7 @@
         <v>2024</v>
       </c>
       <c r="B10" t="s">
-        <v>677</v>
+        <v>695</v>
       </c>
       <c r="C10">
         <v>1708</v>
@@ -7935,7 +8133,7 @@
         <v>2024</v>
       </c>
       <c r="B11" t="s">
-        <v>678</v>
+        <v>696</v>
       </c>
       <c r="C11">
         <v>1827.5</v>
@@ -7955,7 +8153,7 @@
         <v>2024</v>
       </c>
       <c r="B12" t="s">
-        <v>679</v>
+        <v>697</v>
       </c>
       <c r="C12">
         <v>2279</v>
@@ -7975,7 +8173,7 @@
         <v>2024</v>
       </c>
       <c r="B13" t="s">
-        <v>680</v>
+        <v>698</v>
       </c>
       <c r="C13">
         <v>2011.5</v>
@@ -7995,7 +8193,7 @@
         <v>2024</v>
       </c>
       <c r="B14" t="s">
-        <v>669</v>
+        <v>687</v>
       </c>
       <c r="C14">
         <v>2315</v>
@@ -8015,7 +8213,7 @@
         <v>2024</v>
       </c>
       <c r="B15" t="s">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="C15">
         <v>2111</v>
@@ -8035,7 +8233,7 @@
         <v>2024</v>
       </c>
       <c r="B16" t="s">
-        <v>671</v>
+        <v>689</v>
       </c>
       <c r="C16">
         <v>2068</v>
@@ -8055,7 +8253,7 @@
         <v>2024</v>
       </c>
       <c r="B17" t="s">
-        <v>672</v>
+        <v>690</v>
       </c>
       <c r="C17">
         <v>2109</v>
@@ -8075,7 +8273,7 @@
         <v>2024</v>
       </c>
       <c r="B18" t="s">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="C18">
         <v>2031.5</v>
@@ -8095,7 +8293,7 @@
         <v>2024</v>
       </c>
       <c r="B19" t="s">
-        <v>674</v>
+        <v>692</v>
       </c>
       <c r="C19">
         <v>2040</v>
@@ -8115,7 +8313,7 @@
         <v>2024</v>
       </c>
       <c r="B20" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="C20">
         <v>1822</v>
@@ -8135,7 +8333,7 @@
         <v>2024</v>
       </c>
       <c r="B21" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="C21">
         <v>1893</v>
@@ -8155,7 +8353,7 @@
         <v>2025</v>
       </c>
       <c r="B22" t="s">
-        <v>677</v>
+        <v>695</v>
       </c>
       <c r="C22">
         <v>1673</v>
@@ -8175,7 +8373,7 @@
         <v>2025</v>
       </c>
       <c r="B23" t="s">
-        <v>678</v>
+        <v>696</v>
       </c>
       <c r="C23">
         <v>1963</v>
@@ -8195,19 +8393,39 @@
         <v>2025</v>
       </c>
       <c r="B24" t="s">
-        <v>679</v>
+        <v>697</v>
       </c>
       <c r="C24">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="D24">
-        <v>1831.068965517241</v>
+        <v>1830.096774193548</v>
       </c>
       <c r="E24">
         <v>1895</v>
       </c>
       <c r="F24">
         <v>1774</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>2025</v>
+      </c>
+      <c r="B25" t="s">
+        <v>698</v>
+      </c>
+      <c r="C25">
+        <v>1794</v>
+      </c>
+      <c r="D25">
+        <v>1779.8125</v>
+      </c>
+      <c r="E25">
+        <v>1850</v>
+      </c>
+      <c r="F25">
+        <v>1705</v>
       </c>
     </row>
   </sheetData>
@@ -8217,7 +8435,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8570,6 +8788,150 @@
       </c>
       <c r="B44">
         <v>263</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>663</v>
+      </c>
+      <c r="B45">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>664</v>
+      </c>
+      <c r="B46">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>665</v>
+      </c>
+      <c r="B47">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>666</v>
+      </c>
+      <c r="B48">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>667</v>
+      </c>
+      <c r="B49">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>668</v>
+      </c>
+      <c r="B50">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>669</v>
+      </c>
+      <c r="B51">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>670</v>
+      </c>
+      <c r="B52">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>671</v>
+      </c>
+      <c r="B53">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>672</v>
+      </c>
+      <c r="B54">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>673</v>
+      </c>
+      <c r="B55">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>674</v>
+      </c>
+      <c r="B56">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>675</v>
+      </c>
+      <c r="B57">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>676</v>
+      </c>
+      <c r="B58">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>677</v>
+      </c>
+      <c r="B59">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>678</v>
+      </c>
+      <c r="B60">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>679</v>
+      </c>
+      <c r="B61">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>680</v>
+      </c>
+      <c r="B62">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -8579,27 +8941,27 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8607,7 +8969,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>678</v>
+        <v>696</v>
       </c>
       <c r="C2">
         <v>193</v>
@@ -8627,19 +8989,39 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>679</v>
+        <v>697</v>
       </c>
       <c r="C3">
         <v>261</v>
       </c>
       <c r="D3">
-        <v>253.7931034482759</v>
+        <v>254.2258064516129</v>
       </c>
       <c r="E3">
         <v>311</v>
       </c>
       <c r="F3">
         <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="s">
+        <v>698</v>
+      </c>
+      <c r="C4">
+        <v>314</v>
+      </c>
+      <c r="D4">
+        <v>321.9375</v>
+      </c>
+      <c r="E4">
+        <v>375</v>
+      </c>
+      <c r="F4">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -8649,7 +9031,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -9002,6 +9384,150 @@
       </c>
       <c r="B44">
         <v>298</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>663</v>
+      </c>
+      <c r="B45">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>664</v>
+      </c>
+      <c r="B46">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>665</v>
+      </c>
+      <c r="B47">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>666</v>
+      </c>
+      <c r="B48">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>667</v>
+      </c>
+      <c r="B49">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>668</v>
+      </c>
+      <c r="B50">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>669</v>
+      </c>
+      <c r="B51">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>670</v>
+      </c>
+      <c r="B52">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>671</v>
+      </c>
+      <c r="B53">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>672</v>
+      </c>
+      <c r="B54">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>673</v>
+      </c>
+      <c r="B55">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>674</v>
+      </c>
+      <c r="B56">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>675</v>
+      </c>
+      <c r="B57">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>676</v>
+      </c>
+      <c r="B58">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>677</v>
+      </c>
+      <c r="B59">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>678</v>
+      </c>
+      <c r="B60">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>679</v>
+      </c>
+      <c r="B61">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>680</v>
+      </c>
+      <c r="B62">
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -9011,27 +9537,27 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9039,7 +9565,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>678</v>
+        <v>696</v>
       </c>
       <c r="C2">
         <v>187.5</v>
@@ -9059,19 +9585,39 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>679</v>
+        <v>697</v>
       </c>
       <c r="C3">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D3">
-        <v>299.8275862068966</v>
+        <v>299.6774193548387</v>
       </c>
       <c r="E3">
         <v>315</v>
       </c>
       <c r="F3">
         <v>291</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="s">
+        <v>698</v>
+      </c>
+      <c r="C4">
+        <v>338</v>
+      </c>
+      <c r="D4">
+        <v>350.9375</v>
+      </c>
+      <c r="E4">
+        <v>406</v>
+      </c>
+      <c r="F4">
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -9081,7 +9627,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -9434,6 +9980,150 @@
       </c>
       <c r="B44">
         <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>663</v>
+      </c>
+      <c r="B45">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>664</v>
+      </c>
+      <c r="B46">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>665</v>
+      </c>
+      <c r="B47">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>666</v>
+      </c>
+      <c r="B48">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>667</v>
+      </c>
+      <c r="B49">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>668</v>
+      </c>
+      <c r="B50">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>669</v>
+      </c>
+      <c r="B51">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>670</v>
+      </c>
+      <c r="B52">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>671</v>
+      </c>
+      <c r="B53">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>672</v>
+      </c>
+      <c r="B54">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>673</v>
+      </c>
+      <c r="B55">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>674</v>
+      </c>
+      <c r="B56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>675</v>
+      </c>
+      <c r="B57">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>676</v>
+      </c>
+      <c r="B58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>677</v>
+      </c>
+      <c r="B59">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>678</v>
+      </c>
+      <c r="B60">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>679</v>
+      </c>
+      <c r="B61">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>680</v>
+      </c>
+      <c r="B62">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -9443,27 +10133,27 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9471,7 +10161,7 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>678</v>
+        <v>696</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -9491,19 +10181,39 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>679</v>
+        <v>697</v>
       </c>
       <c r="C3">
         <v>61</v>
       </c>
       <c r="D3">
-        <v>61.68965517241379</v>
+        <v>61.70967741935484</v>
       </c>
       <c r="E3">
         <v>73</v>
       </c>
       <c r="F3">
         <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="s">
+        <v>698</v>
+      </c>
+      <c r="C4">
+        <v>55</v>
+      </c>
+      <c r="D4">
+        <v>54.9375</v>
+      </c>
+      <c r="E4">
+        <v>60</v>
+      </c>
+      <c r="F4">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
